--- a/src/make_cv/files/Service/reviews data.xlsx
+++ b/src/make_cv/files/Service/reviews data.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bhelenbr/Codes/make_cv/src/make_cv/files/Service/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D012CF-B93D-964A-9A8C-0D0002E087F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DB2D49-4C74-0242-9395-69B853266E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3460" yWindow="860" windowWidth="25800" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Notes" sheetId="2" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>Journal</t>
   </si>
@@ -29,6 +30,18 @@
   </si>
   <si>
     <t>Rounds</t>
+  </si>
+  <si>
+    <t>This is one way to keep track of reviewing activity on your own.</t>
+  </si>
+  <si>
+    <t>Orcid also keeps track of some reviwing but it is not very complete</t>
+  </si>
+  <si>
+    <t>J. Crystal Growth</t>
+  </si>
+  <si>
+    <t>I prefer to use Web of Science to keep track of reviewing (see instructions)</t>
   </si>
 </sst>
 </file>
@@ -36,7 +49,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -93,10 +106,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,6 +411,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC01FADE-3C60-0E49-B7E9-3A470581FDAE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3">
+        <v>44576</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C9:C12" xr:uid="{995B8B0D-F948-724F-B601-2A533F55D36B}">
+      <formula1>1</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B9:B12" xr:uid="{5A52628E-FA2C-364B-AEA5-10D78CCDD6C4}">
+      <formula1>1</formula1>
+      <formula2>73051</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
